--- a/daily_matches/job_matches_2026-03-11.xlsx
+++ b/daily_matches/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, SQL</t>
+          <t>Data Scientist, RAG, EC2, Glue, Redshift, Kubernetes, CI/CD, Git, Redshift, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3553f5857948933c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Warehousing Specialist</t>
+          <t>Software Engineer III - Java Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Redshift, MLflow, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Redshift, Python</t>
+          <t>RAG, Copilot, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ca5f5e42c7ae45</t>
+          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Product Engineer TS Advanced Therapies</t>
+          <t>Digital S/W Eng Intm Analyst - Officer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e7d20eb0597ce1b</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb0f8c11885ae48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hunter Douglas</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb22f63d0d8fa584</t>
+          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fraud Technology Software Engineer</t>
+          <t>DevOps Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL, SQL, R</t>
+          <t>Generative AI, GCP Vertex AI, Azure ML, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032281f84bc9a278</t>
+          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Sr. Software Engineer - Search (REMOTE)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, S3, Docker, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6644d59ab7ad42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=84a58520eb1a7089</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer (Value Engineering) - Life Sciences</t>
+          <t>Software Development Engineer in Test (SDET I)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Git, Databricks, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be393624199dfd84</t>
+          <t>https://www.indeed.com/viewjob?jk=178d4af05892c6b7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer (Value Engineering) - Public Sector</t>
+          <t>Generative AI Senior Engineer for Guardrails and API Services</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Git, Databricks, Python</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,312 +741,312 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b6724fc23cc36d</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5c95e4c02f0263</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer (Value Engineering) - Energy Industry</t>
+          <t>Software Engineer, I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Git, Databricks, Python</t>
+          <t>RAG, Docker, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f4bcdd1a4f2adb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7e1c47eae592fb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9a1d96797fa9932</t>
+          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f69d8b1d6f42dec</t>
+          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46a005ac08e30129</t>
+          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REMOTE - Data Scientist II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Hadoop, Python, SQL, R</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da756fb0744c38ab</t>
+          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9d3f05f2d1cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Piping Rock Health Products</t>
+          <t>MANTECH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bohemia, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a344026aa847c24d</t>
+          <t>https://www.indeed.com/viewjob?jk=322183339cb49125</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud &amp; Infrastructure Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>MANTECH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b801dbbdaa30c998</t>
+          <t>https://www.indeed.com/viewjob?jk=9061abb2dc3fb744</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deuna</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala, Optimization</t>
+          <t>LangChain, S3, FastAPI, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76827a0ae7f41547</t>
+          <t>https://www.indeed.com/viewjob?jk=e3ee6d1dfe0433a4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Experienced</t>
+          <t>Specialist -Artificial Intelligence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59dd03c7be722425</t>
+          <t>https://www.indeed.com/viewjob?jk=8075973aec6459f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Specialist -Artificial Intelligence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Brightwell</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,392 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d22076ba85b47f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Applied Data Science Specialist</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Child Mind Institute</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9670de71c65970d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Data Science Analyst</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Harlem Children's Zone</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, PostgreSQL, MySQL, MongoDB, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99036511afaa2a9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Escalation Engineer, CDN/Developer Platform</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cloudflare</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e86c4a4bb4d7e5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FujiFilm</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fd45bfe46d8cf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Front-End Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Mochi Health</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cbacb11323e8e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Databases</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Fivetran</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, MongoDB, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=481e36909591dfe8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Equity Intern</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Bessemer Trust</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a0616b488d6109</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr Technical Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PARAMOUNT</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d318de034d90da18</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sr Technical Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PARAMOUNT</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66ebccfe320e27f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Product Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Data Lake, PySpark, Hadoop, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92356017b72bb5cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Ignite Insurance Systems</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Glue, Athena, Redshift, Data Lake, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b9c8e7e8c2c4e17</t>
+          <t>https://www.indeed.com/viewjob?jk=32175977cd7251dd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-11.xlsx
+++ b/daily_matches/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, EC2, Glue, Redshift, Kubernetes, CI/CD, Git, Redshift, MySQL</t>
+          <t>RAG, Glue, Athena, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e55d8f1eb8410b9</t>
+          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java Backend</t>
+          <t>CPU System Validation Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>RAG, TensorFlow, PyTorch, spaCy, NLTK, CI/CD, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,129 +531,129 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f26e792b98c94c</t>
+          <t>https://www.indeed.com/viewjob?jk=377fc2a7cf056710</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Digital S/W Eng Intm Analyst - Officer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb0f8c11885ae48</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabd198cadf6b312</t>
+          <t>https://www.indeed.com/viewjob?jk=73eadbcf00848c6f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Senior Software Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, GCP Vertex AI, Azure ML, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0a8985ab173bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6023aa8f0339c3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Search (REMOTE)</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,69 +661,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a58520eb1a7089</t>
+          <t>https://www.indeed.com/viewjob?jk=f808751afd2350f2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET I)</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178d4af05892c6b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3d672c84a4188e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Generative AI Senior Engineer for Guardrails and API Services</t>
+          <t>AIML Associate - DCL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5c95e4c02f0263</t>
+          <t>https://www.indeed.com/viewjob?jk=b8541dd7149d7a05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, I</t>
+          <t>AIML Sr. Associate - DCL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a7e1c47eae592fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c739373fb5d752b6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a8ca0981290c2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f159d315359abb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da8728e0bd436b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a6072a91eeeca03b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db6e02c8f964c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9abd594d1f62f5b3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f2d15fc950de2e</t>
+          <t>https://www.indeed.com/viewjob?jk=78ba172e8fc4a5fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,169 +941,169 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Git, Kafka, MySQL, MongoDB, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393a7e1ab1bfe7ea</t>
+          <t>https://www.indeed.com/viewjob?jk=da1f7e4ac2bccd6f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MANTECH</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Summit, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322183339cb49125</t>
+          <t>https://www.indeed.com/viewjob?jk=8d421e5a7d5c1696</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MANTECH</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9061abb2dc3fb744</t>
+          <t>https://www.indeed.com/viewjob?jk=d1ca1187146e8137</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, S3, FastAPI, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3ee6d1dfe0433a4</t>
+          <t>https://www.indeed.com/viewjob?jk=74a3d7835099d646</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Specialist -Artificial Intelligence</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8075973aec6459f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f83954958747b1a4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist -Artificial Intelligence</t>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Boston Consulting Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,21 +1112,336 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32175977cd7251dd</t>
+          <t>https://www.indeed.com/viewjob?jk=63c99593a7157706</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=475350c334d31caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cdcbb6ea287579e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11a944799fae2de7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea2cd382123a3335</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d44d6bae1c957683</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bce4a27d3f0540f</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=405303e08b5056c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BCG Platinion | Senior AI Solution Architect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Boston Consulting Group</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a484b2a26068b06d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Marketing Data Analyst</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14695ca4eee60a9c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-11.xlsx
+++ b/daily_matches/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark, Kafka</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843894356ab92a82</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f88eed34169f4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CPU System Validation Architect</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, spaCy, NLTK, CI/CD, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377fc2a7cf056710</t>
+          <t>https://www.indeed.com/viewjob?jk=d200cb704435b8bf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Data Lake, FastAPI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e97823f26b6cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73eadbcf00848c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1e04244359bb9f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6023aa8f0339c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3b25fb23fd56de18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Dhara Consulting Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
+          <t>Generative AI, RAG, PyTorch, Keras, Data Lake, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f808751afd2350f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Developer IV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Git, Kafka, Cassandra, Python, R, Java, Scala, Optimization, Bayesian</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3d672c84a4188e</t>
+          <t>https://www.indeed.com/viewjob?jk=856d67655e437893</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AIML Associate - DCL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8541dd7149d7a05</t>
+          <t>https://www.indeed.com/viewjob?jk=8078d1ebfe9d1942</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AIML Sr. Associate - DCL</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,234 +776,234 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c739373fb5d752b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0772d4beb2dd778b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f159d315359abb</t>
+          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6072a91eeeca03b</t>
+          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9abd594d1f62f5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f25f88e227cb922</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>OCI Terraform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ba172e8fc4a5fb</t>
+          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, Kubernetes, Git, PySpark, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1f7e4ac2bccd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Aon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Summit, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d421e5a7d5c1696</t>
+          <t>https://www.indeed.com/viewjob?jk=b016231514abad5e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>UKG AI Scheduling Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1ca1187146e8137</t>
+          <t>https://www.indeed.com/viewjob?jk=3d7d587ce5d6c4bd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>Senior AI-ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a3d7835099d646</t>
+          <t>https://www.indeed.com/viewjob?jk=f97aecdb14f072ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>Operations Data Analyst, Senior</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,367 +1081,87 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f83954958747b1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c99593a7157706</t>
+          <t>https://www.indeed.com/viewjob?jk=748ff33f7c0f9cd3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
+          <t>Workforce AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Boston Consulting Group</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Git, Databricks, PySpark, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=475350c334d31caa</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Boston Consulting Group</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cdcbb6ea287579e</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Boston Consulting Group</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11a944799fae2de7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Boston Consulting Group</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2cd382123a3335</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Boston Consulting Group</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d44d6bae1c957683</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Boston Consulting Group</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bce4a27d3f0540f</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Boston Consulting Group</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=405303e08b5056c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BCG Platinion | Senior AI Solution Architect</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Boston Consulting Group</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a484b2a26068b06d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Marketing Data Analyst</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Red Hat</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14695ca4eee60a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d6b4c74abeb7c6e1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-11.xlsx
+++ b/daily_matches/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud AI Consultant</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f88eed34169f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb20aa09ee4ee9b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Software Engineer (Ful-Stack &amp; Scientific Visualization)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Applied Research in Acoustics LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,637 +531,112 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d200cb704435b8bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bfbb4d83561f8dbf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Data Lake, FastAPI</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7707ece5dbc064</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe9ffcd47d23e0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.1</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1e04244359bb9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc985e7a360e58c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UKG AI Scheduling Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b25fb23fd56de18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Full Stack AI/ML Engineer (#9BCTLJP00003238)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dhara Consulting Group</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, PyTorch, Keras, Data Lake, Docker, Kubernetes, CI/CD, Git, Databricks</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5fe208cf7f4e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Developer IV</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RealPage Inc</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=856d67655e437893</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8078d1ebfe9d1942</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Java AI / ML Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0772d4beb2dd778b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6614e385cde53c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45938ccd60a0506b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Azure Network Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f25f88e227cb922</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OCI Terraform Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=786a6033717c7e3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, Kubernetes, Git, PySpark, Hadoop, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b17294d4d78b3548</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Aon</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b016231514abad5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>UKG AI Scheduling Consultant</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d587ce5d6c4bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior AI-ML Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f97aecdb14f072ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Operations Data Analyst, Senior</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Pacific Gas and Electric</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=602f4d7955daed21</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=748ff33f7c0f9cd3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Workforce AI &amp; Data Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, PySpark, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6b4c74abeb7c6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0a88c7b2103fc7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-11.xlsx
+++ b/daily_matches/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb20aa09ee4ee9b</t>
+          <t>https://www.indeed.com/viewjob?jk=4789de154dff59e1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer (Ful-Stack &amp; Scientific Visualization)</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Applied Research in Acoustics LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Madison, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Dataflow, MLflow, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,112 +531,2212 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfbb4d83561f8dbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c162c855a415e0aa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>OCI Storage Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Dataflow, MLflow, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe9ffcd47d23e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb5335ce208760e5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc985e7a360e58c</t>
+          <t>https://www.indeed.com/viewjob?jk=b54639551819f0ac</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI-Driven OSINT Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e2885a4f57fb528</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI-Driven OSINT Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Data Lake, FastAPI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85e1a600a644295d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI-Driven OSINT Analyst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, S3, FastAPI, Docker</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f314aef4baf3f7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI-Driven OSINT Analyst</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c593e4d4ed9ba8bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI-Driven OSINT Analyst</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdb3c19b0b102d64</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OCI AI Services Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ba439eac0774c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OCI AI Services Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Data Lake, FastAPI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e10a3388fdc5d76b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OCI AI Services Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7b3f88b90e9cb3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, S3, FastAPI, Docker</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a98d3ffe57a6ab3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Generative AI Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ce63089ab7679bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OCI AI Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cfb8a0fe3be2961</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Hadoop, MySQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a17f9a800db9e079</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer - Databricks &amp; GCP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bafb0baf34406e6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer with Databricks and GCP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1abee21eb63a4b65</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8564f28adedd855e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1d5a3b98413be2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Berwyn, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Gemini, TensorFlow, PyTorch, MLflow, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e37ba368e6b8a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GCP Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e86a9395e17960c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gen AI Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e74b227ccb5a16a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Generative AI Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd5cdde8a2fc3e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst, Digital Growth &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Welltower, Inc</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf337d2c4fd0d06e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Generative AI Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff7e3e96aad3ad0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Microsoft power platform Engineer (Strong expertise in AI Builder, Copilots, Dynamics 365)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0eaa11b39422fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior GCP Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, CI/CD, Terraform, Git, BigQuery</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c4fb2066401756</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, CI/CD, Jenkins, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fafe3bbb6db1d44</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI-Driven OSINT Analyst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbaabd24e0d4a7d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI-Driven OSINT Analyst</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6363625f4344b3b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OCI AI Services Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92e4d50f0b83efe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OCI AI Services Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3978a8c9a90e42e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cloud Engineer - Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f7ef927e38140b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Solr Admin</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b89cfdf469723503</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AWS Platform Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f789c8560e252850</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer (Ful-Stack &amp; Scientific Visualization)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Applied Research in Acoustics LLC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e26d56e21df1acb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Generative AI Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68ec5093a257856a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OCI Cloud Operations Associate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=439aad3226198302</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Docker, CI/CD, Terraform, Git, BigQuery</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e97587e3189309b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AWS API Gateway Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Cortex, EC2, FastAPI, CI/CD, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a95721c90e40065</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>OCI DevOps Professional</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f790d416225ad9b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OCI API Gateway Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4b84fd7269e4e8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Azure Engineer (SRE/DevOps) 1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dd937d6568e8942</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GCP Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f3f59481e80476f</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7936fd607153e13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=613074391bd5ccad</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI-Driven OSINT Analyst</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6fd3f123fa38d24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>REsurety</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Terraform, Snowflake, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=382f9726704381eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cyber Senior Operations Specialist (Senior Engineer – Cloud Security)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=877db3ea0af17ee5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Practicing Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6735ccacec4a1287</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Engineer (Teradata /ETL informatica/Snowflake)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e091ae9d7f7379a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ignition Platform Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96319c25ea9aa90d</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AWS Technical Apprentice / Trainee</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, S3, Kinesis, Docker, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea849db988856cb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Generative AI Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0a88c7b2103fc7</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b688cc0fb511fa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Forum Energy Technologies</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, CI/CD, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e2932ffd73df7be</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=322f0d9e0537c6c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer with Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Power BI, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22ec8bfab0b40259</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SCADA Ignition Developer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c390ef72a71188f</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Digital Manufacturing Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dde29fe5bef6f76</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior SCADA Engineer - Ignition Platform</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=535abbb4f07f0262</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SDET - POS Automation (Retail)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d816bce2e41f8a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>OCI DevOps Professional</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40505304948a5df2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AWS Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e009ebfecb76cc1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, LLaMA, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18ea2ad597e460d1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-11.xlsx
+++ b/daily_matches/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Solutions and Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Glue, Redshift, Data Lake, Kinesis, Git, Snowflake, Redshift</t>
+          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692655d58e016632</t>
+          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, BigQuery, Kinesis, Dataflow, Kubernetes, Apache Airflow, CI/CD, Jenkins</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Redshift, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6675fa52faee21a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8bed4f93581ec1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer with AI/ML</t>
+          <t>Senior Software Engineer I, Fullstack (AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Databricks, MySQL, MongoDB, NoSQL, Tableau, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5769c4ee7b54a55d</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (full-stack)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c56a9ffac444186</t>
+          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Activate Care</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MongoDB, SQL</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8cd994bee806d3</t>
+          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (Remote)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, Hadoop, NoSQL</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5930fa925ff77f76</t>
+          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Kafka, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86de1c1f4587879</t>
+          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d009d7cafef710</t>
+          <t>https://www.indeed.com/viewjob?jk=9d47821e866adbad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Software Engineer - Remote or Hybrid in MN and DC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb7d6f981c89a53</t>
+          <t>https://www.indeed.com/viewjob?jk=d058ceaec01fd027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f54039560a6f8280</t>
+          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Spclst , Software Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Primerica</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>North Wales, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, AWS SageMaker, Data Lake, Kubernetes, Terraform, Tableau, Power BI, Python, R</t>
+          <t>Generative AI, RAG, S3, Redshift, Docker, Kubernetes, CI/CD, Databricks, Redshift, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f9d41b0ab2214b2</t>
+          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr AI/ML DevOps ENG</t>
+          <t>Fullstack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>REBAR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54e9d0a5b26c2c37</t>
+          <t>https://www.indeed.com/viewjob?jk=f684df2a7647c71e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L2)</t>
+          <t>Platform Engineer– Department of Technology – (1043)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>City and County of San Francisco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6140e3faf3473879</t>
+          <t>https://www.indeed.com/viewjob?jk=451ffac950e51457</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Artificial Intelligence (AI) Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Logz.io</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>Generative AI, LLaMA, TensorFlow, PyTorch, spaCy, NLTK, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4abe540963c8be</t>
+          <t>https://www.indeed.com/viewjob?jk=b12e62cdafb76af3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Artificial Intelligence (AI) Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aptitude Health</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, Redshift, Data Lake, Redshift, Python, SQL, R</t>
+          <t>Generative AI, LLaMA, TensorFlow, PyTorch, spaCy, NLTK, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d10e7c01fee4e20</t>
+          <t>https://www.indeed.com/viewjob?jk=d0122b6939ea698b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aptitude Health</t>
+          <t>Strategic Legal Practices</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, Redshift, Data Lake, Redshift, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, Redshift, Redshift, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63fbeab06559ad84</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfa5023d51c0480</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Copilot, Synapse, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b32a96d3a148568b</t>
+          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Cyber Senior Operations Specialist (Senior Engineer – Cloud Security)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326a2430fd4eabc1</t>
+          <t>https://www.indeed.com/viewjob?jk=908c675ba543bca1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Advanced Software Engr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5027e62d0c9af16</t>
+          <t>https://www.indeed.com/viewjob?jk=65a6c1a140615f35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior Software Engineer, Video Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d18b9991a355d07</t>
+          <t>https://www.indeed.com/viewjob?jk=e60a0c81efeb3392</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>Senior AI Defense Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>WilmerHale</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Kubernetes, AKS, CI/CD, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e02142bb3f3c154</t>
+          <t>https://www.indeed.com/viewjob?jk=be08f6828efd2af9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
+          <t>2026 Future Talent Program - Global Pharmaceutical Operations - External Manufacturing Co-Op</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pryon</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,182 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ea9221725ce7d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Infrastructure (DevOps)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Pryon</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c99178b88020f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Zuora</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5890e4a6bcf00fc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer- Remote</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=806313ae3da02a77</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ZoomInfo</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b046d10a603b5537</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Contact Center AI</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, BigQuery, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96141debb61c11cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ece92c03490d364c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-11.xlsx
+++ b/daily_matches/job_matches_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Solutions and Platform Engineer</t>
+          <t>AI Engineer – Clinical AI Platforms (Remote-US)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dea4b70a8571f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=39f196b5f1cbdd13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>AllianceBernstein</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Redshift, Git, Snowflake, Databricks, Redshift</t>
+          <t>RAG, Copilot, Synapse, Docker, Kubernetes, Terraform, Snowflake, Databricks, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8bed4f93581ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d2e68f1134803e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Fullstack (AI)</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Databricks, MySQL, MongoDB, NoSQL, Tableau, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ebdfb86d5d03</t>
+          <t>https://www.indeed.com/viewjob?jk=242ca0eca96622a8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9eb22e24231f22b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6b1bc5d6ff34ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=469d8b6a01022163</t>
+          <t>https://www.indeed.com/viewjob?jk=ced752ad21ecf19c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced1a3a797949e2</t>
+          <t>https://www.indeed.com/viewjob?jk=9487ebdcd79767da</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07382ba85bed2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c25b5e1bc6971185</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Engineer - Applied AI (Java)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, CI/CD, Terraform, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d47821e866adbad</t>
+          <t>https://www.indeed.com/viewjob?jk=9db260ccdb1b82d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote or Hybrid in MN and DC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, MySQL, NoSQL, SQL</t>
+          <t>Data Scientist, RAG, AWS SageMaker, S3, CI/CD, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d058ceaec01fd027</t>
+          <t>https://www.indeed.com/viewjob?jk=0e859cc33a40024c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Kafka, Python, SQL, R</t>
+          <t>LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d0cacdc93f0a17</t>
+          <t>https://www.indeed.com/viewjob?jk=501a40d898b6fecd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Spclst , Software Engineering</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Wales, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Redshift, Docker, Kubernetes, CI/CD, Databricks, Redshift, Python</t>
+          <t>LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463eb478d5ff85bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cd93c42f552234ed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fullstack Engineer</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>REBAR</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f684df2a7647c71e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f9dfd1ebd05b7d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer– Department of Technology – (1043)</t>
+          <t>GenAI Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>City and County of San Francisco</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451ffac950e51457</t>
+          <t>https://www.indeed.com/viewjob?jk=20b4388f15c06e03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LLaMA, TensorFlow, PyTorch, spaCy, NLTK, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b12e62cdafb76af3</t>
+          <t>https://www.indeed.com/viewjob?jk=92690f9d0aceed22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LLaMA, TensorFlow, PyTorch, spaCy, NLTK, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0122b6939ea698b</t>
+          <t>https://www.indeed.com/viewjob?jk=79dfc76ed4b00f60</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Strategic Legal Practices</t>
+          <t>Quantivly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Redshift, Redshift, Tableau, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, FastAPI, Docker, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfa5023d51c0480</t>
+          <t>https://www.indeed.com/viewjob?jk=686431510edbd32e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Developer - Dynamics Contact Center</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Data-Core System, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Middletown, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Synapse, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13618fb171dcc5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=259f41cf671e6faf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cyber Senior Operations Specialist (Senior Engineer – Cloud Security)</t>
+          <t>AWS Developer / Administrator only GC,Citizens or H4 EAD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908c675ba543bca1</t>
+          <t>https://www.indeed.com/viewjob?jk=c93c9f49194a0430</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Advanced Software Engr</t>
+          <t>Senior Application Developers</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CI/CD, GitHub Actions, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a6c1a140615f35</t>
+          <t>https://www.indeed.com/viewjob?jk=315e733bf9be183c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Video Analytics</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ministry Brands</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,77 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60a0c81efeb3392</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior AI Defense Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>WilmerHale</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Kubernetes, AKS, CI/CD, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be08f6828efd2af9</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026 Future Talent Program - Global Pharmaceutical Operations - External Manufacturing Co-Op</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Merck</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Rahway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ece92c03490d364c</t>
+          <t>https://www.indeed.com/viewjob?jk=e37812113b4946c5</t>
         </is>
       </c>
     </row>
